--- a/example_project/SimsList_routing.xlsx
+++ b/example_project/SimsList_routing.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T4"/>
+  <dimension ref="A1:U4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,80 +439,85 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Analyse volumes</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Store hydrographs</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Output suffix</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Input MCDF</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Inflow</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>ELS file</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>SQ file</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>FSL</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>ADV</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>ADV source</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Lake config</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Config file</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Log file</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Output file</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>Hydrographs folder</t>
         </is>
       </c>
-      <c r="S1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>Results folder</t>
         </is>
       </c>
-      <c r="T1" t="inlineStr">
+      <c r="U1" t="inlineStr">
         <is>
           <t>Comment</t>
         </is>
@@ -541,74 +546,79 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>_existing</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>inflows/SYNTHETIC_mc_24h__mcdf.csv</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>inflows/SYNTHETIC_mc_24h_inflows.csv</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>model/SYNTHETIC_juniper.els</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>model/SYNTHETIC_juniper.sq</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>210</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>fsv</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>mcdf</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>sim_options/lake_conditions/lake_config.json</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>sim_options/mc_config.json</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>routed_juniper</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>results/routed_hydrographs</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>results</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>Route the stored inflows through the existing dam</t>
         </is>
@@ -637,74 +647,79 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>_lowered_fsl</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>inflows/SYNTHETIC_mc_24h__mcdf.csv</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>inflows/SYNTHETIC_mc_24h_inflows.csv</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>model/SYNTHETIC_juniper.els</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>model/SYNTHETIC_juniper.sq</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>209</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>fsv</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>mcdf</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>sim_options/lake_conditions/lake_config.json</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>sim_options/mc_config.json</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>routed_juniper</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>results/routed_hydrographs</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>results</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>The same inflows with the full supply level lowered by 1 m</t>
         </is>
@@ -733,74 +748,79 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
           <t>no</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>_varying_adv</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>inflows/SYNTHETIC_mc_24h__mcdf.csv</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>inflows/SYNTHETIC_mc_24h_inflows.csv</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>model/SYNTHETIC_juniper.els</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>model/SYNTHETIC_juniper.sq</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>210</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>fsv</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>lake_z</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>sim_options/lake_conditions/lake_config.json</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>sim_options/mc_config.json</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>routed_juniper</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>results/routed_hydrographs</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>results</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>Existing dam, antecedent volume resampled from lake_z via the lake config</t>
         </is>
